--- a/Design_Files/Stadium_Board/Project Outputs for Stadium_Board/Stadium_Board.xlsx
+++ b/Design_Files/Stadium_Board/Project Outputs for Stadium_Board/Stadium_Board.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28770" windowHeight="14430"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="22140" windowHeight="14430"/>
   </bookViews>
   <sheets>
     <sheet name="Stadium_Board" sheetId="1" r:id="rId1"/>
@@ -149,10 +149,10 @@
     <t>D1, D2</t>
   </si>
   <si>
-    <t>DC-005-25A</t>
-  </si>
-  <si>
-    <t>500mA Jack DCPowerReceptacle 6.4mm 2.5mm 14.2*9.0mm AC/DC Power Connectors ROHS</t>
+    <t>DC-C024E-7A-1.65</t>
+  </si>
+  <si>
+    <t>DC Power Receptacle 1.65mm 4.3mm 7A 24V Plugin AC/DC Power Connectors ROHS</t>
   </si>
   <si>
     <t>J1</t>
@@ -348,7 +348,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -358,6 +358,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFD3D3D3"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -389,7 +395,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -399,6 +405,9 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" quotePrefix="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -717,7 +726,7 @@
       <c r="B2" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="C2" s="3" t="s">
+      <c r="C2" s="5" t="s">
         <v>8</v>
       </c>
       <c r="D2" s="3" t="s">
@@ -737,7 +746,7 @@
       <c r="B3" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C3" s="3" t="s">
+      <c r="C3" s="5" t="s">
         <v>11</v>
       </c>
       <c r="D3" s="3" t="s">
@@ -757,7 +766,7 @@
       <c r="B4" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="C4" s="3" t="s">
+      <c r="C4" s="5" t="s">
         <v>16</v>
       </c>
       <c r="D4" s="3" t="s">
@@ -777,7 +786,7 @@
       <c r="B5" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="C5" s="3" t="s">
+      <c r="C5" s="5" t="s">
         <v>21</v>
       </c>
       <c r="D5" s="3" t="s">
@@ -797,7 +806,7 @@
       <c r="B6" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="C6" s="3" t="s">
+      <c r="C6" s="5" t="s">
         <v>25</v>
       </c>
       <c r="D6" s="3" t="s">
@@ -817,7 +826,7 @@
       <c r="B7" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="C7" s="3" t="s">
+      <c r="C7" s="5" t="s">
         <v>30</v>
       </c>
       <c r="D7" s="3" t="s">
@@ -837,7 +846,7 @@
       <c r="B8" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="C8" s="3" t="s">
+      <c r="C8" s="5" t="s">
         <v>35</v>
       </c>
       <c r="D8" s="3" t="s">
@@ -857,7 +866,7 @@
       <c r="B9" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="C9" s="3" t="s">
+      <c r="C9" s="5" t="s">
         <v>39</v>
       </c>
       <c r="D9" s="3" t="s">
@@ -870,14 +879,14 @@
         <v>2</v>
       </c>
     </row>
-    <row r="10" spans="1:6" ht="90" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:6" ht="75" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
         <v>40</v>
       </c>
       <c r="B10" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="C10" s="3" t="s">
+      <c r="C10" s="5" t="s">
         <v>42</v>
       </c>
       <c r="D10" s="3" t="s">
@@ -897,7 +906,7 @@
       <c r="B11" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="C11" s="3" t="s">
+      <c r="C11" s="5" t="s">
         <v>45</v>
       </c>
       <c r="D11" s="3" t="s">
@@ -917,7 +926,7 @@
       <c r="B12" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="C12" s="3" t="s">
+      <c r="C12" s="5" t="s">
         <v>48</v>
       </c>
       <c r="D12" s="3" t="s">
@@ -937,7 +946,7 @@
       <c r="B13" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="C13" s="3" t="s">
+      <c r="C13" s="5" t="s">
         <v>51</v>
       </c>
       <c r="D13" s="3" t="s">
@@ -957,7 +966,7 @@
       <c r="B14" s="3" t="s">
         <v>54</v>
       </c>
-      <c r="C14" s="3" t="s">
+      <c r="C14" s="5" t="s">
         <v>55</v>
       </c>
       <c r="D14" s="3" t="s">
@@ -977,7 +986,7 @@
       <c r="B15" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="C15" s="3" t="s">
+      <c r="C15" s="5" t="s">
         <v>58</v>
       </c>
       <c r="D15" s="3" t="s">
@@ -997,7 +1006,7 @@
       <c r="B16" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="C16" s="3" t="s">
+      <c r="C16" s="5" t="s">
         <v>63</v>
       </c>
       <c r="D16" s="3" t="s">
@@ -1017,7 +1026,7 @@
       <c r="B17" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="C17" s="3" t="s">
+      <c r="C17" s="5" t="s">
         <v>67</v>
       </c>
       <c r="D17" s="3" t="s">
@@ -1037,7 +1046,7 @@
       <c r="B18" s="3" t="s">
         <v>70</v>
       </c>
-      <c r="C18" s="3" t="s">
+      <c r="C18" s="5" t="s">
         <v>71</v>
       </c>
       <c r="D18" s="3" t="s">
@@ -1057,7 +1066,7 @@
       <c r="B19" s="3" t="s">
         <v>75</v>
       </c>
-      <c r="C19" s="3" t="s">
+      <c r="C19" s="5" t="s">
         <v>76</v>
       </c>
       <c r="D19" s="3" t="s">
@@ -1077,7 +1086,7 @@
       <c r="B20" s="3" t="s">
         <v>80</v>
       </c>
-      <c r="C20" s="3" t="s">
+      <c r="C20" s="5" t="s">
         <v>81</v>
       </c>
       <c r="D20" s="3" t="s">
@@ -1097,7 +1106,7 @@
       <c r="B21" s="3" t="s">
         <v>85</v>
       </c>
-      <c r="C21" s="3" t="s">
+      <c r="C21" s="5" t="s">
         <v>86</v>
       </c>
       <c r="D21" s="3" t="s">
@@ -1117,7 +1126,7 @@
       <c r="B22" s="3" t="s">
         <v>88</v>
       </c>
-      <c r="C22" s="3" t="s">
+      <c r="C22" s="5" t="s">
         <v>89</v>
       </c>
       <c r="D22" s="3" t="s">
@@ -1137,7 +1146,7 @@
       <c r="B23" s="3" t="s">
         <v>92</v>
       </c>
-      <c r="C23" s="3" t="s">
+      <c r="C23" s="5" t="s">
         <v>93</v>
       </c>
       <c r="D23" s="3" t="s">
@@ -1157,7 +1166,7 @@
       <c r="B24" s="3" t="s">
         <v>96</v>
       </c>
-      <c r="C24" s="3" t="s">
+      <c r="C24" s="5" t="s">
         <v>97</v>
       </c>
       <c r="D24" s="3" t="s">
@@ -1177,7 +1186,7 @@
       <c r="B25" s="3" t="s">
         <v>100</v>
       </c>
-      <c r="C25" s="3" t="s">
+      <c r="C25" s="5" t="s">
         <v>101</v>
       </c>
       <c r="D25" s="3" t="s">
